--- a/Proyecto/Program_CheckList_Web.xlsx
+++ b/Proyecto/Program_CheckList_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Repositories\ServicesDevelopment\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2B5683-C9E1-40EC-BEF1-6993F28118C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1DD28F-CEE0-4C69-B2ED-51905920C896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,7 +523,7 @@
         <v>0.5</v>
       </c>
       <c r="D3" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -551,7 +551,7 @@
       <c r="C5" s="6"/>
       <c r="D5" s="12">
         <f>SUM(D2:D4)</f>
-        <v>3.0454545454545454</v>
+        <v>3.2454545454545451</v>
       </c>
       <c r="E5" s="6"/>
     </row>
